--- a/site/exports/nju-astronomy-space-science.xlsx
+++ b/site/exports/nju-astronomy-space-science.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：日球物理导论；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科三年级；来源ID：nju-cx-profile；https://astronomy.nju.edu.cn/people/cx.html | 科学之光青年系列：走进太阳风暴；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科一年级；来源ID：nju-cx-profile；https://astronomy.nju.edu.cn/people/cx.html | Hot topics in Astrophysics；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：Level 3, Spring；来源教学时期：历史CV所列，具体教学年未知；来源ID：nju-cx-mps-cv；https://www.mps.mpg.de/5858346 | Introduction to Space Physics；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：Level 3, Fall；来源教学时期：历史CV所列，具体教学年未知；来源ID：nju-cx-mps-cv；https://www.mps.mpg.de/5858346</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：日球物理导论；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科三年级；来源ID：nju-cx-profile；https://astronomy.nju.edu.cn/people/cx.html | 科学之光青年系列：走进太阳风暴；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科一年级；来源ID：nju-cx-profile；https://astronomy.nju.edu.cn/people/cx.html | Hot topics in Astrophysics；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：Level 3, Spring；来源教学时期：历史CV所列，具体教学年未知；来源ID：nju-cx-mps-cv；https://www.mps.mpg.de/5858346 | Introduction to Space Physics；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：Level 3, Fall；来源教学时期：历史CV所列，具体教学年未知；来源ID：nju-cx-mps-cv；https://www.mps.mpg.de/5858346；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：新生研讨课；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科一年级；来源ID：nju-cpf-profile；https://astronomy.nju.edu.cn/people/cpf.html | 天文文献阅读；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生一年级；来源ID：nju-cpf-profile；https://astronomy.nju.edu.cn/people/cpf.html | 计算天文；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生；来源ID：nju-cpf-profile；https://astronomy.nju.edu.cn/people/cpf.html</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：新生研讨课；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科一年级；来源ID：nju-cpf-profile；https://astronomy.nju.edu.cn/people/cpf.html | 天文文献阅读；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生一年级；来源ID：nju-cpf-profile；https://astronomy.nju.edu.cn/people/cpf.html | 计算天文；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生；来源ID：nju-cpf-profile；https://astronomy.nju.edu.cn/people/cpf.html；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：天体物理辐射理论；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生必修；来源ID：nju-cy-profile；https://astronomy.nju.edu.cn/people/cy.html | 星际介质物理；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生必修；来源ID：nju-cy-profile；https://astronomy.nju.edu.cn/people/cy.html | 流体力学；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科必修；来源ID：nju-cy-profile；https://astronomy.nju.edu.cn/people/cy.html</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：天体物理辐射理论；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生必修；来源ID：nju-cy-profile；https://astronomy.nju.edu.cn/people/cy.html | 星际介质物理；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：研究生必修；来源ID：nju-cy-profile；https://astronomy.nju.edu.cn/people/cy.html | 流体力学；角色未披露；教学／课程开设时间：时间未披露；来源课程层次：本科必修；来源ID：nju-cy-profile；https://astronomy.nju.edu.cn/people/cy.html；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
